--- a/408/OS/2024/ModularAutomation/reports/payloads.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/payloads.xlsx
@@ -19,139 +19,197 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
-  <si>
-    <t>;touch /root/占位符;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
   <si>
     <t>#END_OF_ROW</t>
   </si>
   <si>
-    <t>&gt; /root/占位符.c</t>
-  </si>
-  <si>
-    <t>[touch /root/占位符]</t>
-  </si>
-  <si>
-    <t>\ntouch /root/占位符\n</t>
-  </si>
-  <si>
-    <t>\rtouch /root/占位符\r</t>
-  </si>
-  <si>
-    <t>`touch /root/占位符`</t>
-  </si>
-  <si>
-    <t>$(touch /root/占位符)$</t>
-  </si>
-  <si>
-    <t>&amp;(touch /root/占位符)&amp;</t>
-  </si>
-  <si>
-    <t>|touch /root/占位符|</t>
-  </si>
-  <si>
-    <t>cat /etc/passwd &gt; /root/占位符.txt</t>
-  </si>
-  <si>
-    <t>cat /etc/passwd &lt; /root/占位符.txt</t>
-  </si>
-  <si>
-    <t>*touch /root/占位符*</t>
-  </si>
-  <si>
-    <t>%touch /root/占位符%</t>
-  </si>
-  <si>
-    <t>^touch /root/占位符^</t>
-  </si>
-  <si>
-    <t>!touch /root/占位符!</t>
-  </si>
-  <si>
-    <t>#touch /root/占位符#</t>
-  </si>
-  <si>
-    <t>@touch /root/占位符@</t>
-  </si>
-  <si>
-    <t>*(touch /root/占位符)*</t>
-  </si>
-  <si>
-    <t>%(touch /root/占位符)%</t>
-  </si>
-  <si>
-    <t>^(touch /root/占位符)^</t>
-  </si>
-  <si>
-    <t>!(touch /root/占位符)!</t>
-  </si>
-  <si>
-    <t>#(touch /root/占位符)#</t>
-  </si>
-  <si>
-    <t>echo&lt;/root/占位符</t>
-  </si>
-  <si>
-    <t>echo&gt;/root/占位符</t>
-  </si>
-  <si>
-    <t>;touch /root/占位符;'</t>
-  </si>
-  <si>
-    <t>cat /etc/passwd &gt; /root/占位符.txt'</t>
-  </si>
-  <si>
-    <t>$(touch /root/占位符)$'</t>
-  </si>
-  <si>
-    <t>&amp;(touch /root/占位符)&amp;'</t>
-  </si>
-  <si>
-    <t>|touch /root/占位符|'</t>
-  </si>
-  <si>
-    <t>\ntouch /root/占位符\n'</t>
-  </si>
-  <si>
-    <t>\rtouch /root/占位符\r''</t>
-  </si>
-  <si>
-    <t>`touch /root/占位符`'</t>
-  </si>
-  <si>
-    <t>';touch /root/占位符;'</t>
-  </si>
-  <si>
-    <t>'cat /etc/passwd &gt; /root/占位符.txt'</t>
-  </si>
-  <si>
-    <t>'$(touch /root/占位符)$'</t>
-  </si>
-  <si>
-    <t>'&amp;(touch /root/占位符)&amp;'</t>
-  </si>
-  <si>
-    <t>'|touch /root/占位符|'</t>
-  </si>
-  <si>
-    <t>'\ntouch /root/占位符\n'</t>
-  </si>
-  <si>
-    <t>'\rtouch /root/占位符\r''</t>
-  </si>
-  <si>
-    <t>'`touch /root/占位符`'</t>
-  </si>
-  <si>
     <t>#END_OF_COL</t>
+  </si>
+  <si>
+    <t>占位符</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>\\n\\necho&gt;占位符</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>;touch 占位符;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[touch 占位符]</t>
+  </si>
+  <si>
+    <t>\ntouch 占位符\n</t>
+  </si>
+  <si>
+    <t>\rtouch 占位符\r</t>
+  </si>
+  <si>
+    <t>`touch 占位符`</t>
+  </si>
+  <si>
+    <t>$(touch 占位符)$</t>
+  </si>
+  <si>
+    <t>&amp;(touch 占位符)&amp;</t>
+  </si>
+  <si>
+    <t>|touch 占位符|</t>
+  </si>
+  <si>
+    <t>*touch 占位符*</t>
+  </si>
+  <si>
+    <t>%touch 占位符%</t>
+  </si>
+  <si>
+    <t>^touch 占位符^</t>
+  </si>
+  <si>
+    <t>!touch 占位符!</t>
+  </si>
+  <si>
+    <t>#touch 占位符#</t>
+  </si>
+  <si>
+    <t>*(touch 占位符)*</t>
+  </si>
+  <si>
+    <t>%(touch 占位符)%</t>
+  </si>
+  <si>
+    <t>^(touch 占位符)^</t>
+  </si>
+  <si>
+    <t>!(touch 占位符)!</t>
+  </si>
+  <si>
+    <t>#(touch 占位符)#</t>
+  </si>
+  <si>
+    <t>echo&lt;占位符</t>
+  </si>
+  <si>
+    <t>echo&gt;占位符</t>
+  </si>
+  <si>
+    <t>;touch 占位符;'</t>
+  </si>
+  <si>
+    <t>$(touch 占位符)$'</t>
+  </si>
+  <si>
+    <t>&amp;(touch 占位符)&amp;'</t>
+  </si>
+  <si>
+    <t>|touch 占位符|'</t>
+  </si>
+  <si>
+    <t>\ntouch 占位符\n'</t>
+  </si>
+  <si>
+    <t>\rtouch 占位符\r''</t>
+  </si>
+  <si>
+    <t>`touch 占位符`'</t>
+  </si>
+  <si>
+    <t>';touch 占位符;'</t>
+  </si>
+  <si>
+    <t>'$(touch 占位符)$'</t>
+  </si>
+  <si>
+    <t>'&amp;(touch 占位符)&amp;'</t>
+  </si>
+  <si>
+    <t>'|touch 占位符|'</t>
+  </si>
+  <si>
+    <t>'\ntouch 占位符\n'</t>
+  </si>
+  <si>
+    <t>'\rtouch 占位符\r''</t>
+  </si>
+  <si>
+    <t>'`touch 占位符`'</t>
+  </si>
+  <si>
+    <t>@touch 占位符@</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 占位符</t>
+  </si>
+  <si>
+    <t>'cat 占位符 &gt; 占位符'</t>
+  </si>
+  <si>
+    <t>cat 占位符 &gt; 占位符</t>
+  </si>
+  <si>
+    <t>cat 占位符 &lt; 占位符</t>
+  </si>
+  <si>
+    <t>cat 占位符 &gt; 占位符'</t>
+  </si>
+  <si>
+    <t>\\ntouch 占位符\\n'</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rtouch 占位符\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r''</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +226,13 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -210,6 +275,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -521,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="41.125" style="1" customWidth="1"/>
@@ -530,90 +601,90 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
+      <c r="A10" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
+      <c r="A11" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -621,7 +692,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -629,7 +700,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -637,7 +708,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -645,7 +716,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -653,211 +724,247 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
+      <c r="A17" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
-        <v>26</v>
+      <c r="A26" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="4" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="4" t="s">
-        <v>33</v>
+      <c r="A33" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
-        <v>36</v>
+      <c r="A36" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>1</v>
+      <c r="B45" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A43" r:id="rId1" display="\\n\\necho&gt;1234"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/408/OS/2024/ModularAutomation/reports/payloads.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/payloads.xlsx
@@ -1,42 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RjDir\admin_d95c8884-f44c-4529-8f3b-48d5788371c1\Downloads\业务文档\NPEE\408\OS\2024\ModularAutomation\reports\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22185" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="#TEMP" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
   <si>
+    <t>;touch 占位符;</t>
+  </si>
+  <si>
     <t>#END_OF_ROW</t>
   </si>
   <si>
-    <t>#END_OF_COL</t>
-  </si>
-  <si>
-    <t>占位符</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>\\n\\necho&gt;占位符</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>;touch 占位符;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>&gt; 占位符</t>
   </si>
   <si>
     <t>[touch 占位符]</t>
@@ -60,6 +59,12 @@
     <t>|touch 占位符|</t>
   </si>
   <si>
+    <t>cat 占位符 &gt; 占位符</t>
+  </si>
+  <si>
+    <t>cat 占位符 &lt; 占位符</t>
+  </si>
+  <si>
     <t>*touch 占位符*</t>
   </si>
   <si>
@@ -75,6 +80,9 @@
     <t>#touch 占位符#</t>
   </si>
   <si>
+    <t>@touch 占位符@</t>
+  </si>
+  <si>
     <t>*(touch 占位符)*</t>
   </si>
   <si>
@@ -99,6 +107,9 @@
     <t>;touch 占位符;'</t>
   </si>
   <si>
+    <t>cat 占位符 &gt; 占位符'</t>
+  </si>
+  <si>
     <t>$(touch 占位符)$'</t>
   </si>
   <si>
@@ -111,64 +122,25 @@
     <t>\ntouch 占位符\n'</t>
   </si>
   <si>
+    <t>\\ntouch 占位符\\n'</t>
+  </si>
+  <si>
     <t>\rtouch 占位符\r''</t>
   </si>
   <si>
-    <t>`touch 占位符`'</t>
-  </si>
-  <si>
-    <t>';touch 占位符;'</t>
-  </si>
-  <si>
-    <t>'$(touch 占位符)$'</t>
-  </si>
-  <si>
-    <t>'&amp;(touch 占位符)&amp;'</t>
-  </si>
-  <si>
-    <t>'|touch 占位符|'</t>
-  </si>
-  <si>
-    <t>'\ntouch 占位符\n'</t>
-  </si>
-  <si>
-    <t>'\rtouch 占位符\r''</t>
-  </si>
-  <si>
-    <t>'`touch 占位符`'</t>
-  </si>
-  <si>
-    <t>@touch 占位符@</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt; 占位符</t>
-  </si>
-  <si>
-    <t>'cat 占位符 &gt; 占位符'</t>
-  </si>
-  <si>
-    <t>cat 占位符 &gt; 占位符</t>
-  </si>
-  <si>
-    <t>cat 占位符 &lt; 占位符</t>
-  </si>
-  <si>
-    <t>cat 占位符 &gt; 占位符'</t>
-  </si>
-  <si>
-    <t>\\ntouch 占位符\\n'</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>\</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -187,7 +159,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -202,14 +173,55 @@
       </rPr>
       <t>r''</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>`touch 占位符`'</t>
+  </si>
+  <si>
+    <t>';touch 占位符;'</t>
+  </si>
+  <si>
+    <t>'cat 占位符 &gt; 占位符'</t>
+  </si>
+  <si>
+    <t>'$(touch 占位符)$'</t>
+  </si>
+  <si>
+    <t>'&amp;(touch 占位符)&amp;'</t>
+  </si>
+  <si>
+    <t>'|touch 占位符|'</t>
+  </si>
+  <si>
+    <t>'\ntouch 占位符\n'</t>
+  </si>
+  <si>
+    <t>'\rtouch 占位符\r''</t>
+  </si>
+  <si>
+    <t>'`touch 占位符`'</t>
+  </si>
+  <si>
+    <t>\\n\\necho&gt;占位符</t>
+  </si>
+  <si>
+    <t>占位符</t>
+  </si>
+  <si>
+    <t>#END_OF_COL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,20 +236,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -250,8 +393,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -259,11 +588,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,32 +845,70 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="FF000000"/>
+      <color rgb="00000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -586,105 +1195,105 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="41.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="41.1296296296296" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="5" t="s">
-        <v>39</v>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="B11" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -692,7 +1301,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -700,7 +1309,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -708,7 +1317,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -716,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -724,247 +1333,247 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
+      <c r="A17" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
+      <c r="A26" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="6" t="s">
-        <v>45</v>
+      <c r="A33" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
+      <c r="A36" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A43" r:id="rId1" display="\\n\\necho&gt;1234"/>
+    <hyperlink ref="A43" r:id="rId1" display="\\n\\necho&gt;占位符"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/408/OS/2024/ModularAutomation/reports/payloads.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/payloads.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="47">
+  <si>
+    <t>\"'} ; 占位符 ; '\"</t>
+  </si>
+  <si>
+    <t>#END_OF_ROW</t>
+  </si>
   <si>
     <t>;touch 占位符;</t>
-  </si>
-  <si>
-    <t>#END_OF_ROW</t>
   </si>
   <si>
     <t>&gt; 占位符</t>
@@ -834,15 +837,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -1201,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="41.1296296296296" style="1" customWidth="1"/>
@@ -1217,7 +1223,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1225,7 +1231,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1233,7 +1239,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1241,7 +1247,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1249,7 +1255,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1257,7 +1263,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1265,7 +1271,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1273,7 +1279,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1281,7 +1287,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1289,7 +1295,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1297,7 +1303,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1305,7 +1311,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1313,7 +1319,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1321,7 +1327,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1329,7 +1335,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1337,7 +1343,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1345,7 +1351,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1353,7 +1359,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1361,7 +1367,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1369,7 +1375,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1377,7 +1383,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1385,7 +1391,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1393,7 +1399,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1409,7 +1415,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -1417,7 +1423,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -1425,7 +1431,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -1433,7 +1439,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -1441,7 +1447,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -1449,7 +1455,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -1457,7 +1463,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -1465,7 +1471,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -1473,7 +1479,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -1481,7 +1487,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -1489,7 +1495,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -1497,7 +1503,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -1505,7 +1511,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -1513,7 +1519,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -1521,7 +1527,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -1529,7 +1535,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -1537,7 +1543,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -1545,7 +1551,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -1553,7 +1559,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -1561,16 +1567,24 @@
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A43" r:id="rId1" display="\\n\\necho&gt;占位符"/>
+    <hyperlink ref="A44" r:id="rId1" display="\\n\\necho&gt;占位符"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
